--- a/objects.xlsx
+++ b/objects.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2РАБОТА\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2РАБОТА\moscow-objects-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470D868C-E0BB-4975-A3EB-C9630F5FCDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61337594-B57A-49D4-BC8C-9FE519CDF695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FE6A299-EFA8-4276-B2C7-1769C47EC51A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Комментарий</t>
   </si>
   <si>
-    <t>Ферст Скул</t>
-  </si>
-  <si>
     <t>ИТП</t>
   </si>
   <si>
@@ -75,28 +72,28 @@
     <t>Ежемесячное ТО</t>
   </si>
   <si>
-    <t>Медцентр МГУ</t>
-  </si>
-  <si>
-    <t>Вентиляция</t>
-  </si>
-  <si>
     <t>Петров</t>
   </si>
   <si>
     <t>ТО</t>
   </si>
   <si>
-    <t>г. Москва, ул.Веерная 24</t>
-  </si>
-  <si>
-    <t>г. Москва,Мичуринский проспект 45</t>
-  </si>
-  <si>
     <t>Широта</t>
   </si>
   <si>
     <t>Долгота</t>
+  </si>
+  <si>
+    <t>ЛФ Мехор</t>
+  </si>
+  <si>
+    <t>г. Москва, Новый Арбат,11с1</t>
+  </si>
+  <si>
+    <t>ООО Прямые Инвестиции</t>
+  </si>
+  <si>
+    <t>г. Москва, ул.Веерная 24Г</t>
   </si>
 </sst>
 </file>
@@ -468,6 +465,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -496,10 +494,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -507,63 +505,63 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="2">
         <v>79999999999</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="I2" s="2">
-        <v>55.752000000000002</v>
+        <v>55.752085000000001</v>
       </c>
       <c r="J2" s="2">
-        <v>37.606999999999999</v>
+        <v>37.596237000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>79999999999</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I3" s="2">
-        <v>55.752000000000002</v>
+        <v>55.708627999999997</v>
       </c>
       <c r="J3" s="2">
-        <v>37.606999999999999</v>
+        <v>37.484836999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -578,5 +576,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/objects.xlsx
+++ b/objects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2РАБОТА\moscow-objects-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61337594-B57A-49D4-BC8C-9FE519CDF695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DFF82B-3FD6-43D2-94BC-4ECE3C635281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FE6A299-EFA8-4276-B2C7-1769C47EC51A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +84,9 @@
     <t>Долгота</t>
   </si>
   <si>
+    <t>ИП Авин</t>
+  </si>
+  <si>
     <t>ЛФ Мехор</t>
   </si>
   <si>
@@ -94,6 +97,21 @@
   </si>
   <si>
     <t>г. Москва, ул.Веерная 24Г</t>
+  </si>
+  <si>
+    <t>г. Москва, Проспект Мира,119с324</t>
+  </si>
+  <si>
+    <t>ООО Клаустрофобия</t>
+  </si>
+  <si>
+    <t>ООО Смарт Климат</t>
+  </si>
+  <si>
+    <t>г. Москва, Проспект Мира,119с548</t>
+  </si>
+  <si>
+    <t>г. Москва, Проспект Мира,119с501</t>
   </si>
 </sst>
 </file>
@@ -461,11 +479,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A495D7-BC26-44EA-869A-093C1E9BEBD2}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -505,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -537,10 +556,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -564,15 +583,101 @@
         <v>37.484836999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+    <row r="4" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2">
+        <v>79999999999</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>55.836706</v>
+      </c>
+      <c r="J4">
+        <v>37.626519999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
+        <v>79999999999</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>55.825204999999997</v>
+      </c>
+      <c r="J5">
+        <v>37636444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
+        <v>79999999999</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2">
+        <v>55.827084999999997</v>
+      </c>
+      <c r="J6" s="2">
+        <v>37.632395000000002</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/objects.xlsx
+++ b/objects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2РАБОТА\moscow-objects-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DFF82B-3FD6-43D2-94BC-4ECE3C635281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED77BA31-7AF6-479A-81D0-59A7C5AE025B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FE6A299-EFA8-4276-B2C7-1769C47EC51A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -69,15 +69,9 @@
     <t>Действующий</t>
   </si>
   <si>
-    <t>Ежемесячное ТО</t>
-  </si>
-  <si>
     <t>Петров</t>
   </si>
   <si>
-    <t>ТО</t>
-  </si>
-  <si>
     <t>Широта</t>
   </si>
   <si>
@@ -112,6 +106,21 @@
   </si>
   <si>
     <t>г. Москва, Проспект Мира,119с501</t>
+  </si>
+  <si>
+    <t>Раз в месяц</t>
+  </si>
+  <si>
+    <t>79165706920 - Александр</t>
+  </si>
+  <si>
+    <t>79619008809 -  Егор</t>
+  </si>
+  <si>
+    <t>79036186869 - Андрей Петрович</t>
+  </si>
+  <si>
+    <t>79166096983 - Андрей</t>
   </si>
 </sst>
 </file>
@@ -513,10 +522,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -524,10 +533,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -535,14 +544,14 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2">
-        <v>79999999999</v>
+      <c r="F2" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I2" s="2">
         <v>55.752085000000001</v>
@@ -556,25 +565,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2">
-        <v>79999999999</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I3" s="2">
         <v>55.708627999999997</v>
@@ -588,10 +597,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
@@ -599,14 +608,14 @@
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2">
-        <v>79999999999</v>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I4">
         <v>55.836706</v>
@@ -620,10 +629,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -631,20 +640,20 @@
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2">
-        <v>79999999999</v>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I5">
         <v>55.825204999999997</v>
       </c>
       <c r="J5">
-        <v>37636444</v>
+        <v>37.636443999999997</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="72" x14ac:dyDescent="0.3">
@@ -652,10 +661,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -663,14 +672,14 @@
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="2">
-        <v>79999999999</v>
+      <c r="F6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I6" s="2">
         <v>55.827084999999997</v>
